--- a/self-rag/documents/DBLog.xlsx
+++ b/self-rag/documents/DBLog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sajal\Project\Agentic AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sajal\Project\Agentic AI\self-rag\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECEAC4A-317A-40B0-A9A1-D9461F277E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E1A903-7E14-42E0-B7E9-A50E97944FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -748,8 +748,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1159,7 +1162,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1169,7 +1172,7 @@
       <c r="C8" t="s">
         <v>6</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1229,7 +1232,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -1239,7 +1242,7 @@
       <c r="C13" t="s">
         <v>6</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>30</v>
       </c>
     </row>
